--- a/Adv_excel/sales_pivort_26_8-sept.xlsx
+++ b/Adv_excel/sales_pivort_26_8-sept.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0FA44234EE9B2914/Desktop/tops/TTS_DA/Adv_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{9C666655-80E7-46C8-A980-F219F27D4FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BEE632D-5041-4FDA-BA85-B27AAD3C5D4F}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{9C666655-80E7-46C8-A980-F219F27D4FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8632E3B-5955-4E65-B04F-7DB39B8C64C9}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2800" yWindow="2800" windowWidth="7500" windowHeight="6000" firstSheet="3" activeTab="8" xr2:uid="{7E5669FC-4505-4B32-9B2D-82EAEC5DACF9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="9" xr2:uid="{7E5669FC-4505-4B32-9B2D-82EAEC5DACF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="graphs" sheetId="11" r:id="rId7"/>
     <sheet name="8-sept-26" sheetId="10" r:id="rId8"/>
     <sheet name="Sheet11" sheetId="12" r:id="rId9"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId10"/>
+    <sheet name="Sheet13" sheetId="14" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Region">#N/A</definedName>
@@ -30,14 +31,14 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId11"/>
-    <pivotCache cacheId="47" r:id="rId12"/>
+    <pivotCache cacheId="23" r:id="rId12"/>
+    <pivotCache cacheId="47" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="170">
   <si>
     <t>Order_ID</t>
   </si>
@@ -586,6 +587,15 @@
   </si>
   <si>
     <t>07-Sep</t>
+  </si>
+  <si>
+    <t>spend</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>sd</t>
   </si>
 </sst>
 </file>
@@ -7093,6 +7103,83 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6399C9-2A11-44DC-A74F-E3D822BD8E63}">
+  <dimension ref="D1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="3" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="4" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10">
+        <f>AVERAGE(D2:D8)</f>
+        <v>1575.7142857142858</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11">
+        <f>VAR(D2:D8)</f>
+        <v>321128.57142857154</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12">
+        <f>STDEV(D2:D8)</f>
+        <v>566.68207261971111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD7A29E-AD3D-4A65-A5D1-47CDE797A43F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
